--- a/output/pdf_financials_xlsx/PHRM.xlsx
+++ b/output/pdf_financials_xlsx/PHRM.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.20682</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.186697</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.059869</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.416319</v>
+        <v>-6.623139</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.11534</v>
+        <v>-3.302037</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.526106</v>
+        <v>-1.585975</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.414897</v>
+        <v>-6.621717</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.114629</v>
+        <v>-3.301326</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.526106</v>
+        <v>-1.585975</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>5.919808</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.133231</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.923213</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>5.919808</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.133231</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.923213</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6.253141</v>
+        <v>0.333333</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.315046</v>
+        <v>0.181815</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.123213</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="49">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
